--- a/output/YASKAWA_NEW_SHIPMENT_REVIEW.xlsx
+++ b/output/YASKAWA_NEW_SHIPMENT_REVIEW.xlsx
@@ -858,7 +858,7 @@
       </c>
       <c r="O2" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P2" s="68" t="n">
@@ -920,7 +920,7 @@
       </c>
       <c r="O3" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P3" s="68" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="O4" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P4" s="68" t="n">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="O5" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P5" s="68" t="n">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="O6" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P6" s="68" t="n">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="O7" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P7" s="68" t="n">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P8" s="68" t="n">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="O9" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P9" s="68" t="n">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="O10" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P10" s="68" t="n">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="O11" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P11" s="68" t="n">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O12" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P12" s="68" t="n">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="O13" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P13" s="68" t="n">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="O14" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P14" s="68" t="n">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="O15" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P15" s="68" t="n">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="O16" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P16" s="68" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="O17" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P17" s="68" t="n">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="O18" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P18" s="68" t="n">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="O19" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P19" s="68" t="n">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O20" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P20" s="68" t="n">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="O21" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P21" s="68" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="O22" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P22" s="68" t="n">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="O23" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P23" s="68" t="n">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="O24" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P24" s="68" t="n">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="O25" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P25" s="68" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="O26" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P26" s="68" t="n">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="O27" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P27" s="68" t="n">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="O28" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P28" s="68" t="n">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="O29" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P29" s="68" t="n">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="O30" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P30" s="68" t="n">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="O31" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P31" s="68" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="O32" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P32" s="68" t="n">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="O33" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P33" s="68" t="n">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="O34" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P34" s="68" t="n">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="O35" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P35" s="68" t="n">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="O36" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P36" s="68" t="n">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="O37" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P37" s="68" t="n">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="O38" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P38" s="68" t="n">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O39" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P39" s="68" t="n">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="O40" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P40" s="68" t="n">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="O41" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P41" s="68" t="n">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="O42" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P42" s="68" t="n">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="O43" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P43" s="68" t="n">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="O44" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P44" s="68" t="n">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="O45" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P45" s="68" t="n">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="O46" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P46" s="68" t="n">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="O47" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P47" s="68" t="n">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="O48" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P48" s="68" t="n">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="O49" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P49" s="68" t="n">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="O50" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P50" s="68" t="n">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="O51" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P51" s="68" t="n">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="O52" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P52" s="68" t="n">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="O53" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P53" s="68" t="n">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="O54" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P54" s="68" t="n">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="O55" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P55" s="68" t="n">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="O56" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P56" s="68" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="O57" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P57" s="68" t="n">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O58" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P58" s="68" t="n">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="O59" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P59" s="68" t="n">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="O60" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P60" s="68" t="n">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="O61" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P61" s="68" t="n">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="O62" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P62" s="68" t="n">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="O63" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P63" s="68" t="n">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="O64" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P64" s="68" t="n">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="O65" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P65" s="68" t="n">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O66" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P66" s="68" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="O67" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P67" s="68" t="n">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="O68" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P68" s="68" t="n">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="O69" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P69" s="68" t="n">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="O70" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P70" s="68" t="n">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="O71" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P71" s="68" t="n">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="O72" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P72" s="68" t="n">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="O73" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P73" s="68" t="n">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="O74" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P74" s="68" t="n">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="O75" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P75" s="68" t="n">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="O76" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P76" s="68" t="n">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O77" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P77" s="68" t="n">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="O78" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P78" s="68" t="n">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="O79" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P79" s="68" t="n">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="O80" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P80" s="68" t="n">
@@ -5764,7 +5764,7 @@
       </c>
       <c r="O81" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P81" s="68" t="n">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="O82" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P82" s="68" t="n">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="O83" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P83" s="68" t="n">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="O84" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P84" s="68" t="n">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O85" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P85" s="68" t="n">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="O86" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P86" s="68" t="n">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="O87" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P87" s="68" t="n">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="O88" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P88" s="68" t="n">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="O89" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P89" s="68" t="n">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="O90" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P90" s="68" t="n">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="O91" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P91" s="68" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="O92" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P92" s="68" t="n">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="O93" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P93" s="68" t="n">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="O94" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P94" s="68" t="n">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="O95" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P95" s="68" t="n">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="O96" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P96" s="68" t="n">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="O97" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P97" s="68" t="n">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="O98" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P98" s="68" t="n">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="O99" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P99" s="68" t="n">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="O100" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P100" s="68" t="n">
@@ -7004,7 +7004,7 @@
       </c>
       <c r="O101" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P101" s="68" t="n">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="O102" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P102" s="68" t="n">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="O103" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P103" s="68" t="n">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="O104" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P104" s="68" t="n">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="O105" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P105" s="68" t="n">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="O106" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P106" s="68" t="n">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="O107" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P107" s="68" t="n">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="O108" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P108" s="68" t="n">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="O109" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P109" s="68" t="n">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="O110" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P110" s="68" t="n">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="O111" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P111" s="68" t="n">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O112" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P112" s="68" t="n">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="O113" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P113" s="68" t="n">
@@ -7810,7 +7810,7 @@
       </c>
       <c r="O114" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P114" s="68" t="n">
@@ -7872,7 +7872,7 @@
       </c>
       <c r="O115" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P115" s="68" t="n">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="O116" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P116" s="68" t="n">
@@ -7996,7 +7996,7 @@
       </c>
       <c r="O117" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P117" s="68" t="n">
@@ -8058,7 +8058,7 @@
       </c>
       <c r="O118" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P118" s="68" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="O119" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P119" s="68" t="n">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="O120" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P120" s="68" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="O121" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P121" s="68" t="n">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="O122" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P122" s="68" t="n">
@@ -8368,7 +8368,7 @@
       </c>
       <c r="O123" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P123" s="68" t="n">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="O124" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P124" s="68" t="n">
@@ -8492,7 +8492,7 @@
       </c>
       <c r="O125" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P125" s="68" t="n">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="O126" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P126" s="68" t="n">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="O127" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P127" s="68" t="n">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="O128" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P128" s="68" t="n">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="O129" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P129" s="68" t="n">
@@ -8802,7 +8802,7 @@
       </c>
       <c r="O130" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P130" s="68" t="n">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="O131" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P131" s="68" t="n">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="O132" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P132" s="68" t="n">
@@ -8988,7 +8988,7 @@
       </c>
       <c r="O133" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P133" s="68" t="n">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="O134" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P134" s="68" t="n">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="O135" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P135" s="68" t="n">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="O136" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P136" s="68" t="n">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="O137" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P137" s="68" t="n">
@@ -9298,7 +9298,7 @@
       </c>
       <c r="O138" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P138" s="68" t="n">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="O139" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P139" s="68" t="n">
@@ -9422,7 +9422,7 @@
       </c>
       <c r="O140" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P140" s="68" t="n">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="O141" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P141" s="68" t="n">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="O142" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P142" s="68" t="n">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="O143" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P143" s="68" t="n">
@@ -9670,7 +9670,7 @@
       </c>
       <c r="O144" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P144" s="68" t="n">
@@ -9732,7 +9732,7 @@
       </c>
       <c r="O145" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P145" s="68" t="n">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="O146" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P146" s="68" t="n">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="O147" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P147" s="68" t="n">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="O148" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P148" s="68" t="n">
@@ -9980,7 +9980,7 @@
       </c>
       <c r="O149" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P149" s="68" t="n">
@@ -10042,7 +10042,7 @@
       </c>
       <c r="O150" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P150" s="68" t="n">
@@ -10104,7 +10104,7 @@
       </c>
       <c r="O151" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P151" s="68" t="n">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="O152" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P152" s="68" t="n">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="O153" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P153" s="68" t="n">
@@ -10290,7 +10290,7 @@
       </c>
       <c r="O154" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P154" s="68" t="n">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="O155" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P155" s="68" t="n">
@@ -10414,7 +10414,7 @@
       </c>
       <c r="O156" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P156" s="68" t="n">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="O157" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P157" s="68" t="n">
@@ -10538,7 +10538,7 @@
       </c>
       <c r="O158" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P158" s="68" t="n">
@@ -10600,7 +10600,7 @@
       </c>
       <c r="O159" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P159" s="68" t="n">
@@ -10662,7 +10662,7 @@
       </c>
       <c r="O160" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P160" s="68" t="n">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="O161" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P161" s="68" t="n">
@@ -10786,7 +10786,7 @@
       </c>
       <c r="O162" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P162" s="68" t="n">
@@ -10848,7 +10848,7 @@
       </c>
       <c r="O163" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P163" s="68" t="n">
@@ -10910,7 +10910,7 @@
       </c>
       <c r="O164" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P164" s="68" t="n">
@@ -10972,7 +10972,7 @@
       </c>
       <c r="O165" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P165" s="68" t="n">
@@ -11034,7 +11034,7 @@
       </c>
       <c r="O166" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P166" s="68" t="n">
@@ -11096,7 +11096,7 @@
       </c>
       <c r="O167" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P167" s="68" t="n">
@@ -11158,7 +11158,7 @@
       </c>
       <c r="O168" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P168" s="68" t="n">
@@ -11220,7 +11220,7 @@
       </c>
       <c r="O169" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P169" s="68" t="n">
@@ -11282,7 +11282,7 @@
       </c>
       <c r="O170" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P170" s="68" t="n">
@@ -11344,7 +11344,7 @@
       </c>
       <c r="O171" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P171" s="68" t="n">
@@ -11406,7 +11406,7 @@
       </c>
       <c r="O172" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P172" s="68" t="n">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="O173" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P173" s="68" t="n">
@@ -11530,7 +11530,7 @@
       </c>
       <c r="O174" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P174" s="68" t="n">
@@ -11592,7 +11592,7 @@
       </c>
       <c r="O175" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P175" s="68" t="n">
@@ -11654,7 +11654,7 @@
       </c>
       <c r="O176" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P176" s="68" t="n">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="O177" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P177" s="68" t="n">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="O178" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P178" s="68" t="n">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="O179" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P179" s="68" t="n">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="O180" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P180" s="68" t="n">
@@ -11964,7 +11964,7 @@
       </c>
       <c r="O181" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P181" s="68" t="n">
@@ -12026,7 +12026,7 @@
       </c>
       <c r="O182" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P182" s="68" t="n">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="O183" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P183" s="68" t="n">
@@ -12150,7 +12150,7 @@
       </c>
       <c r="O184" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P184" s="68" t="n">
@@ -12212,7 +12212,7 @@
       </c>
       <c r="O185" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P185" s="68" t="n">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="O186" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P186" s="68" t="n">
@@ -12336,7 +12336,7 @@
       </c>
       <c r="O187" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P187" s="68" t="n">
@@ -12398,7 +12398,7 @@
       </c>
       <c r="O188" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P188" s="68" t="n">
@@ -12460,7 +12460,7 @@
       </c>
       <c r="O189" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P189" s="68" t="n">
@@ -12522,7 +12522,7 @@
       </c>
       <c r="O190" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
       <c r="P190" s="68" t="n">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="O191" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P191" s="68" t="n">
@@ -12646,7 +12646,7 @@
       </c>
       <c r="O192" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P192" s="68" t="n">
@@ -12708,7 +12708,7 @@
       </c>
       <c r="O193" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P193" s="68" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="O194" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P194" s="68" t="n">
@@ -12832,7 +12832,7 @@
       </c>
       <c r="O195" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P195" s="68" t="n">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="O196" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P196" s="68" t="n">
@@ -12956,7 +12956,7 @@
       </c>
       <c r="O197" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P197" s="68" t="n">
@@ -13018,7 +13018,7 @@
       </c>
       <c r="O198" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P198" s="68" t="n">
@@ -13080,7 +13080,7 @@
       </c>
       <c r="O199" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P199" s="68" t="n">
@@ -13142,7 +13142,7 @@
       </c>
       <c r="O200" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P200" s="68" t="n">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="O201" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P201" s="68" t="n">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="O202" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P202" s="68" t="n">
@@ -13328,7 +13328,7 @@
       </c>
       <c r="O203" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P203" s="68" t="n">
@@ -13390,7 +13390,7 @@
       </c>
       <c r="O204" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P204" s="68" t="n">
@@ -13452,7 +13452,7 @@
       </c>
       <c r="O205" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P205" s="68" t="n">
@@ -13514,7 +13514,7 @@
       </c>
       <c r="O206" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P206" s="68" t="n">
@@ -13576,7 +13576,7 @@
       </c>
       <c r="O207" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P207" s="68" t="n">
@@ -13638,7 +13638,7 @@
       </c>
       <c r="O208" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P208" s="68" t="n">
@@ -13700,7 +13700,7 @@
       </c>
       <c r="O209" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P209" s="68" t="n">
@@ -13762,7 +13762,7 @@
       </c>
       <c r="O210" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P210" s="68" t="n">
@@ -13824,7 +13824,7 @@
       </c>
       <c r="O211" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P211" s="68" t="n">
@@ -13886,7 +13886,7 @@
       </c>
       <c r="O212" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P212" s="68" t="n">
@@ -13948,7 +13948,7 @@
       </c>
       <c r="O213" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P213" s="68" t="n">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="O214" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P214" s="68" t="n">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="O215" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P215" s="68" t="n">
@@ -14134,7 +14134,7 @@
       </c>
       <c r="O216" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P216" s="68" t="n">
@@ -14196,7 +14196,7 @@
       </c>
       <c r="O217" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P217" s="68" t="n">
@@ -14258,7 +14258,7 @@
       </c>
       <c r="O218" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P218" s="68" t="n">
@@ -14320,7 +14320,7 @@
       </c>
       <c r="O219" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P219" s="68" t="n">
@@ -14382,7 +14382,7 @@
       </c>
       <c r="O220" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P220" s="68" t="n">
@@ -14444,7 +14444,7 @@
       </c>
       <c r="O221" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P221" s="68" t="n">
@@ -14506,7 +14506,7 @@
       </c>
       <c r="O222" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P222" s="68" t="n">
@@ -14568,7 +14568,7 @@
       </c>
       <c r="O223" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P223" s="68" t="n">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="O224" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P224" s="68" t="n">
@@ -14692,7 +14692,7 @@
       </c>
       <c r="O225" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P225" s="68" t="n">
@@ -14754,7 +14754,7 @@
       </c>
       <c r="O226" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P226" s="68" t="n">
@@ -14816,7 +14816,7 @@
       </c>
       <c r="O227" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P227" s="68" t="n">
@@ -14882,7 +14882,7 @@
       </c>
       <c r="O228" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P228" s="68" t="n">
@@ -14948,7 +14948,7 @@
       </c>
       <c r="O229" s="69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
       <c r="P229" s="68" t="n">
@@ -39562,7 +39562,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39579,7 +39579,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39600,7 +39600,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39621,7 +39621,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39638,7 +39638,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39655,7 +39655,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39672,7 +39672,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39689,7 +39689,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39706,7 +39706,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39723,7 +39723,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39740,7 +39740,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39757,7 +39757,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39774,7 +39774,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39791,7 +39791,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39808,7 +39808,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39825,7 +39825,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39842,7 +39842,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39859,7 +39859,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39876,7 +39876,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39893,7 +39893,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39910,7 +39910,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39927,7 +39927,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39944,7 +39944,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39961,7 +39961,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39978,7 +39978,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -39995,7 +39995,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40012,7 +40012,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40029,7 +40029,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40046,7 +40046,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40063,7 +40063,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40080,7 +40080,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40097,7 +40097,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40114,7 +40114,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40131,7 +40131,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40148,7 +40148,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40165,7 +40165,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40182,7 +40182,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40199,7 +40199,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40216,7 +40216,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40233,7 +40233,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40250,7 +40250,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40267,7 +40267,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40284,7 +40284,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40301,7 +40301,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40318,7 +40318,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40335,7 +40335,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40352,7 +40352,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40369,7 +40369,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40386,7 +40386,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40403,7 +40403,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40420,7 +40420,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40437,7 +40437,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40454,7 +40454,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40471,7 +40471,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40488,7 +40488,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40505,7 +40505,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40522,7 +40522,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40539,7 +40539,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40556,7 +40556,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40573,7 +40573,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40590,7 +40590,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40607,7 +40607,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40624,7 +40624,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40641,7 +40641,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40658,7 +40658,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40675,7 +40675,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40692,7 +40692,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40709,7 +40709,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40726,7 +40726,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40743,7 +40743,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40760,7 +40760,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40777,7 +40777,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40794,7 +40794,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40811,7 +40811,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40828,7 +40828,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40845,7 +40845,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40862,7 +40862,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40879,7 +40879,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40896,7 +40896,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40913,7 +40913,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40930,7 +40930,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40947,7 +40947,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40964,7 +40964,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40981,7 +40981,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -40998,7 +40998,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41015,7 +41015,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41032,7 +41032,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41049,7 +41049,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41066,7 +41066,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41083,7 +41083,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41100,7 +41100,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41117,7 +41117,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41134,7 +41134,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41151,7 +41151,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41168,7 +41168,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41185,7 +41185,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41202,7 +41202,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41219,7 +41219,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41236,7 +41236,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41253,7 +41253,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41270,7 +41270,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41287,7 +41287,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41304,7 +41304,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41321,7 +41321,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41338,7 +41338,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41355,7 +41355,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41372,7 +41372,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41389,7 +41389,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41406,7 +41406,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41423,7 +41423,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41440,7 +41440,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41457,7 +41457,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41474,7 +41474,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41491,7 +41491,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41508,7 +41508,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41525,7 +41525,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41542,7 +41542,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41559,7 +41559,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41576,7 +41576,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41593,7 +41593,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41610,7 +41610,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41627,7 +41627,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41644,7 +41644,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41661,7 +41661,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41678,7 +41678,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41695,7 +41695,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41712,7 +41712,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41729,7 +41729,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41746,7 +41746,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41763,7 +41763,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41780,7 +41780,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41797,7 +41797,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41814,7 +41814,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41831,7 +41831,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41848,7 +41848,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41865,7 +41865,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41882,7 +41882,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41899,7 +41899,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41916,7 +41916,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41933,7 +41933,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41950,7 +41950,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41967,7 +41967,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -41984,7 +41984,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42001,7 +42001,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42018,7 +42018,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42035,7 +42035,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42052,7 +42052,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42069,7 +42069,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42086,7 +42086,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42103,7 +42103,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42120,7 +42120,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42137,7 +42137,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42154,7 +42154,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42171,7 +42171,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42188,7 +42188,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42205,7 +42205,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42222,7 +42222,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42239,7 +42239,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42256,7 +42256,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42273,7 +42273,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42290,7 +42290,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42307,7 +42307,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42324,7 +42324,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42341,7 +42341,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42358,7 +42358,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42375,7 +42375,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42392,7 +42392,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42409,7 +42409,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42426,7 +42426,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42443,7 +42443,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42460,7 +42460,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42477,7 +42477,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42494,7 +42494,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42511,7 +42511,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42528,7 +42528,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42545,7 +42545,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42562,7 +42562,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42579,7 +42579,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42596,7 +42596,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42613,7 +42613,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42630,7 +42630,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42647,7 +42647,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42664,7 +42664,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42681,7 +42681,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42698,7 +42698,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42715,7 +42715,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42732,7 +42732,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42749,7 +42749,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42766,7 +42766,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>PO/V/712</t>
         </is>
       </c>
     </row>
@@ -42783,7 +42783,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -42800,7 +42800,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -42817,7 +42817,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -42834,7 +42834,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -42851,7 +42851,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -42868,7 +42868,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -42885,7 +42885,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -42902,7 +42902,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -42919,7 +42919,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -42936,7 +42936,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -42953,7 +42953,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -42970,7 +42970,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -42987,7 +42987,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43004,7 +43004,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43021,7 +43021,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43038,7 +43038,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43055,7 +43055,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43072,7 +43072,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43089,7 +43089,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43106,7 +43106,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43123,7 +43123,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43140,7 +43140,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43157,7 +43157,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43174,7 +43174,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43191,7 +43191,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43208,7 +43208,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43225,7 +43225,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43242,7 +43242,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43259,7 +43259,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43276,7 +43276,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43293,7 +43293,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43310,7 +43310,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43327,7 +43327,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43344,7 +43344,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43361,7 +43361,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43378,7 +43378,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43395,7 +43395,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43416,7 +43416,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>
@@ -43437,7 +43437,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>wer</t>
         </is>
       </c>
     </row>

--- a/output/YASKAWA_NEW_SHIPMENT_REVIEW.xlsx
+++ b/output/YASKAWA_NEW_SHIPMENT_REVIEW.xlsx
@@ -835,7 +835,7 @@
       </c>
       <c r="H2" s="69" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC)</t>
+          <t>955-CO00MO00 - VIPASetCard 001 (VSC)</t>
         </is>
       </c>
       <c r="I2" s="69" t="n">
@@ -858,11 +858,11 @@
       </c>
       <c r="O2" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/705</t>
         </is>
       </c>
       <c r="P2" s="68" t="n">
-        <v>46316</v>
+        <v>46140</v>
       </c>
     </row>
     <row r="3">
@@ -897,7 +897,7 @@
       </c>
       <c r="H3" s="69" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC)</t>
+          <t>955-CO00MO00 - VIPASetCard 001 (VSC)</t>
         </is>
       </c>
       <c r="I3" s="69" t="n">
@@ -920,11 +920,11 @@
       </c>
       <c r="O3" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/705</t>
         </is>
       </c>
       <c r="P3" s="68" t="n">
-        <v>46316</v>
+        <v>46140</v>
       </c>
     </row>
     <row r="4">
@@ -986,11 +986,11 @@
       </c>
       <c r="O4" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/708</t>
         </is>
       </c>
       <c r="P4" s="68" t="n">
-        <v>46316</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="5">
@@ -1052,11 +1052,11 @@
       </c>
       <c r="O5" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/708</t>
         </is>
       </c>
       <c r="P5" s="68" t="n">
-        <v>46316</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="6">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H6" s="69" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC)</t>
+          <t>955-CO000MO00 - VIPASetCard 001 (VSC)</t>
         </is>
       </c>
       <c r="I6" s="69" t="n">
@@ -1114,11 +1114,11 @@
       </c>
       <c r="O6" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/710</t>
         </is>
       </c>
       <c r="P6" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="7">
@@ -1176,11 +1176,11 @@
       </c>
       <c r="O7" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P7" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="8">
@@ -1238,11 +1238,11 @@
       </c>
       <c r="O8" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P8" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="9">
@@ -1300,11 +1300,11 @@
       </c>
       <c r="O9" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P9" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="10">
@@ -1362,11 +1362,11 @@
       </c>
       <c r="O10" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P10" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="11">
@@ -1424,11 +1424,11 @@
       </c>
       <c r="O11" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P11" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="12">
@@ -1486,11 +1486,11 @@
       </c>
       <c r="O12" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P12" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="13">
@@ -1548,11 +1548,11 @@
       </c>
       <c r="O13" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P13" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="14">
@@ -1610,11 +1610,11 @@
       </c>
       <c r="O14" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P14" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="15">
@@ -1672,11 +1672,11 @@
       </c>
       <c r="O15" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P15" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="16">
@@ -1734,11 +1734,11 @@
       </c>
       <c r="O16" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P16" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="17">
@@ -1796,11 +1796,11 @@
       </c>
       <c r="O17" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P17" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="18">
@@ -1858,11 +1858,11 @@
       </c>
       <c r="O18" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P18" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="19">
@@ -1920,11 +1920,11 @@
       </c>
       <c r="O19" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P19" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="20">
@@ -1982,11 +1982,11 @@
       </c>
       <c r="O20" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P20" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="21">
@@ -2044,11 +2044,11 @@
       </c>
       <c r="O21" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P21" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="22">
@@ -2106,11 +2106,11 @@
       </c>
       <c r="O22" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P22" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="23">
@@ -2168,11 +2168,11 @@
       </c>
       <c r="O23" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P23" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="24">
@@ -2230,11 +2230,11 @@
       </c>
       <c r="O24" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P24" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="25">
@@ -2292,11 +2292,11 @@
       </c>
       <c r="O25" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P25" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="26">
@@ -2354,11 +2354,11 @@
       </c>
       <c r="O26" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P26" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="27">
@@ -2416,11 +2416,11 @@
       </c>
       <c r="O27" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P27" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="28">
@@ -2478,11 +2478,11 @@
       </c>
       <c r="O28" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P28" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="29">
@@ -2540,11 +2540,11 @@
       </c>
       <c r="O29" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P29" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="30">
@@ -2602,11 +2602,11 @@
       </c>
       <c r="O30" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P30" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="31">
@@ -2664,11 +2664,11 @@
       </c>
       <c r="O31" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P31" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="32">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="H32" s="69" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC)</t>
+          <t>955-CO00M00 - VIPASetCard 001 (VSC)</t>
         </is>
       </c>
       <c r="I32" s="69" t="n">
@@ -2726,11 +2726,11 @@
       </c>
       <c r="O32" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
       <c r="P32" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="33">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="H33" s="69" t="inlineStr">
         <is>
-          <t>315-4NE23 -VIPA CPU 315SN</t>
+          <t>315-4NE23 - VIPA CPU 315SN</t>
         </is>
       </c>
       <c r="I33" s="69" t="n">
@@ -2788,11 +2788,11 @@
       </c>
       <c r="O33" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/717</t>
         </is>
       </c>
       <c r="P33" s="68" t="n">
-        <v>46316</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="34">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="H34" s="69" t="inlineStr">
         <is>
-          <t>315-4NE23 -VIPA CPU 315SN</t>
+          <t>315-4NE23 - VIPA CPU 315SN</t>
         </is>
       </c>
       <c r="I34" s="69" t="n">
@@ -2850,11 +2850,11 @@
       </c>
       <c r="O34" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/717</t>
         </is>
       </c>
       <c r="P34" s="68" t="n">
-        <v>46316</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="35">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="P35" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="36">
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="P36" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="37">
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="P37" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="38">
@@ -3102,7 +3102,7 @@
         </is>
       </c>
       <c r="P38" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="39">
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="P39" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="40">
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="P40" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="41">
@@ -3288,7 +3288,7 @@
         </is>
       </c>
       <c r="P41" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="42">
@@ -3350,7 +3350,7 @@
         </is>
       </c>
       <c r="P42" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="43">
@@ -3412,7 +3412,7 @@
         </is>
       </c>
       <c r="P43" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="44">
@@ -3474,7 +3474,7 @@
         </is>
       </c>
       <c r="P44" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="45">
@@ -3536,7 +3536,7 @@
         </is>
       </c>
       <c r="P45" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="46">
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="P46" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="47">
@@ -3660,7 +3660,7 @@
         </is>
       </c>
       <c r="P47" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="48">
@@ -3722,7 +3722,7 @@
         </is>
       </c>
       <c r="P48" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="49">
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="P49" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="50">
@@ -3846,7 +3846,7 @@
         </is>
       </c>
       <c r="P50" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="51">
@@ -3908,7 +3908,7 @@
         </is>
       </c>
       <c r="P51" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="52">
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="P52" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="53">
@@ -4032,7 +4032,7 @@
         </is>
       </c>
       <c r="P53" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="54">
@@ -4094,7 +4094,7 @@
         </is>
       </c>
       <c r="P54" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="55">
@@ -4156,7 +4156,7 @@
         </is>
       </c>
       <c r="P55" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="56">
@@ -4218,7 +4218,7 @@
         </is>
       </c>
       <c r="P56" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="57">
@@ -4280,7 +4280,7 @@
         </is>
       </c>
       <c r="P57" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="58">
@@ -4342,7 +4342,7 @@
         </is>
       </c>
       <c r="P58" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="59">
@@ -4404,7 +4404,7 @@
         </is>
       </c>
       <c r="P59" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="60">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="H60" s="69" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC)</t>
+          <t>955-COO00MO00 - VIPASetCard 001 (VSC)</t>
         </is>
       </c>
       <c r="I60" s="69" t="n">
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="P60" s="68" t="n">
-        <v>46316</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="61">
@@ -4524,11 +4524,11 @@
       </c>
       <c r="O61" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P61" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="62">
@@ -4586,11 +4586,11 @@
       </c>
       <c r="O62" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P62" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="63">
@@ -4648,11 +4648,11 @@
       </c>
       <c r="O63" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P63" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="64">
@@ -4710,11 +4710,11 @@
       </c>
       <c r="O64" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P64" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="65">
@@ -4772,11 +4772,11 @@
       </c>
       <c r="O65" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P65" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="66">
@@ -4834,11 +4834,11 @@
       </c>
       <c r="O66" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P66" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="67">
@@ -4896,11 +4896,11 @@
       </c>
       <c r="O67" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P67" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="68">
@@ -4958,11 +4958,11 @@
       </c>
       <c r="O68" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P68" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="69">
@@ -5020,11 +5020,11 @@
       </c>
       <c r="O69" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P69" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="70">
@@ -5082,11 +5082,11 @@
       </c>
       <c r="O70" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P70" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="71">
@@ -5144,11 +5144,11 @@
       </c>
       <c r="O71" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P71" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="72">
@@ -5206,11 +5206,11 @@
       </c>
       <c r="O72" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P72" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="73">
@@ -5268,11 +5268,11 @@
       </c>
       <c r="O73" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P73" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="74">
@@ -5330,11 +5330,11 @@
       </c>
       <c r="O74" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P74" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="75">
@@ -5392,11 +5392,11 @@
       </c>
       <c r="O75" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P75" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="76">
@@ -5454,11 +5454,11 @@
       </c>
       <c r="O76" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P76" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="77">
@@ -5516,11 +5516,11 @@
       </c>
       <c r="O77" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P77" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="78">
@@ -5578,11 +5578,11 @@
       </c>
       <c r="O78" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P78" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="79">
@@ -5640,11 +5640,11 @@
       </c>
       <c r="O79" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P79" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="80">
@@ -5702,11 +5702,11 @@
       </c>
       <c r="O80" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P80" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="81">
@@ -5764,11 +5764,11 @@
       </c>
       <c r="O81" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P81" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="82">
@@ -5826,11 +5826,11 @@
       </c>
       <c r="O82" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P82" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="83">
@@ -5888,11 +5888,11 @@
       </c>
       <c r="O83" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P83" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="84">
@@ -5950,11 +5950,11 @@
       </c>
       <c r="O84" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P84" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="85">
@@ -6012,11 +6012,11 @@
       </c>
       <c r="O85" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P85" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="86">
@@ -6074,11 +6074,11 @@
       </c>
       <c r="O86" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P86" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="87">
@@ -6136,11 +6136,11 @@
       </c>
       <c r="O87" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P87" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="88">
@@ -6198,11 +6198,11 @@
       </c>
       <c r="O88" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P88" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="89">
@@ -6260,11 +6260,11 @@
       </c>
       <c r="O89" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P89" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="90">
@@ -6322,11 +6322,11 @@
       </c>
       <c r="O90" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P90" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="91">
@@ -6384,11 +6384,11 @@
       </c>
       <c r="O91" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P91" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="92">
@@ -6446,11 +6446,11 @@
       </c>
       <c r="O92" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P92" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="93">
@@ -6508,11 +6508,11 @@
       </c>
       <c r="O93" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P93" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="94">
@@ -6570,11 +6570,11 @@
       </c>
       <c r="O94" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P94" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="95">
@@ -6632,11 +6632,11 @@
       </c>
       <c r="O95" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P95" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="96">
@@ -6694,11 +6694,11 @@
       </c>
       <c r="O96" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P96" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="97">
@@ -6756,11 +6756,11 @@
       </c>
       <c r="O97" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P97" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="98">
@@ -6818,11 +6818,11 @@
       </c>
       <c r="O98" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P98" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="99">
@@ -6880,11 +6880,11 @@
       </c>
       <c r="O99" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P99" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="100">
@@ -6942,11 +6942,11 @@
       </c>
       <c r="O100" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P100" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="101">
@@ -7004,11 +7004,11 @@
       </c>
       <c r="O101" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P101" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="102">
@@ -7066,11 +7066,11 @@
       </c>
       <c r="O102" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P102" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="103">
@@ -7128,11 +7128,11 @@
       </c>
       <c r="O103" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P103" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="104">
@@ -7190,11 +7190,11 @@
       </c>
       <c r="O104" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P104" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="105">
@@ -7252,11 +7252,11 @@
       </c>
       <c r="O105" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P105" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="106">
@@ -7314,11 +7314,11 @@
       </c>
       <c r="O106" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P106" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="107">
@@ -7376,11 +7376,11 @@
       </c>
       <c r="O107" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P107" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="108">
@@ -7438,11 +7438,11 @@
       </c>
       <c r="O108" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P108" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="109">
@@ -7500,11 +7500,11 @@
       </c>
       <c r="O109" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P109" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="110">
@@ -7562,11 +7562,11 @@
       </c>
       <c r="O110" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P110" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="111">
@@ -7624,11 +7624,11 @@
       </c>
       <c r="O111" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P111" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="112">
@@ -7686,11 +7686,11 @@
       </c>
       <c r="O112" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P112" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="113">
@@ -7748,11 +7748,11 @@
       </c>
       <c r="O113" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P113" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="114">
@@ -7810,11 +7810,11 @@
       </c>
       <c r="O114" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P114" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="115">
@@ -7872,11 +7872,11 @@
       </c>
       <c r="O115" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P115" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="116">
@@ -7934,11 +7934,11 @@
       </c>
       <c r="O116" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P116" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="117">
@@ -7996,11 +7996,11 @@
       </c>
       <c r="O117" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P117" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="118">
@@ -8058,11 +8058,11 @@
       </c>
       <c r="O118" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P118" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="119">
@@ -8120,11 +8120,11 @@
       </c>
       <c r="O119" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P119" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="120">
@@ -8182,11 +8182,11 @@
       </c>
       <c r="O120" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P120" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="121">
@@ -8244,11 +8244,11 @@
       </c>
       <c r="O121" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P121" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="122">
@@ -8306,11 +8306,11 @@
       </c>
       <c r="O122" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P122" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="123">
@@ -8368,11 +8368,11 @@
       </c>
       <c r="O123" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P123" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="124">
@@ -8430,11 +8430,11 @@
       </c>
       <c r="O124" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P124" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="125">
@@ -8492,11 +8492,11 @@
       </c>
       <c r="O125" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P125" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="126">
@@ -8554,11 +8554,11 @@
       </c>
       <c r="O126" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P126" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="127">
@@ -8616,11 +8616,11 @@
       </c>
       <c r="O127" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P127" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="128">
@@ -8678,11 +8678,11 @@
       </c>
       <c r="O128" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P128" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="129">
@@ -8740,11 +8740,11 @@
       </c>
       <c r="O129" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P129" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="130">
@@ -8802,11 +8802,11 @@
       </c>
       <c r="O130" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P130" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="131">
@@ -8864,11 +8864,11 @@
       </c>
       <c r="O131" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P131" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="132">
@@ -8926,11 +8926,11 @@
       </c>
       <c r="O132" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P132" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="133">
@@ -8988,11 +8988,11 @@
       </c>
       <c r="O133" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P133" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="134">
@@ -9050,11 +9050,11 @@
       </c>
       <c r="O134" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P134" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="135">
@@ -9112,11 +9112,11 @@
       </c>
       <c r="O135" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P135" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="136">
@@ -9174,11 +9174,11 @@
       </c>
       <c r="O136" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P136" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="137">
@@ -9236,11 +9236,11 @@
       </c>
       <c r="O137" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P137" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="138">
@@ -9298,11 +9298,11 @@
       </c>
       <c r="O138" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P138" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="139">
@@ -9360,11 +9360,11 @@
       </c>
       <c r="O139" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P139" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="140">
@@ -9422,11 +9422,11 @@
       </c>
       <c r="O140" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P140" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="141">
@@ -9484,11 +9484,11 @@
       </c>
       <c r="O141" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P141" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="142">
@@ -9546,11 +9546,11 @@
       </c>
       <c r="O142" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P142" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="143">
@@ -9608,11 +9608,11 @@
       </c>
       <c r="O143" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P143" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="144">
@@ -9670,11 +9670,11 @@
       </c>
       <c r="O144" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P144" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="145">
@@ -9732,11 +9732,11 @@
       </c>
       <c r="O145" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P145" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="146">
@@ -9794,11 +9794,11 @@
       </c>
       <c r="O146" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P146" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="147">
@@ -9856,11 +9856,11 @@
       </c>
       <c r="O147" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P147" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="148">
@@ -9918,11 +9918,11 @@
       </c>
       <c r="O148" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P148" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="149">
@@ -9980,11 +9980,11 @@
       </c>
       <c r="O149" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P149" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="150">
@@ -10042,11 +10042,11 @@
       </c>
       <c r="O150" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P150" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="151">
@@ -10104,11 +10104,11 @@
       </c>
       <c r="O151" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P151" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="152">
@@ -10166,11 +10166,11 @@
       </c>
       <c r="O152" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P152" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="153">
@@ -10228,11 +10228,11 @@
       </c>
       <c r="O153" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P153" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="154">
@@ -10290,11 +10290,11 @@
       </c>
       <c r="O154" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P154" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="155">
@@ -10352,11 +10352,11 @@
       </c>
       <c r="O155" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P155" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="156">
@@ -10414,11 +10414,11 @@
       </c>
       <c r="O156" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P156" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="157">
@@ -10476,11 +10476,11 @@
       </c>
       <c r="O157" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P157" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="158">
@@ -10538,11 +10538,11 @@
       </c>
       <c r="O158" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P158" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="159">
@@ -10600,11 +10600,11 @@
       </c>
       <c r="O159" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P159" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="160">
@@ -10662,11 +10662,11 @@
       </c>
       <c r="O160" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P160" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="161">
@@ -10724,11 +10724,11 @@
       </c>
       <c r="O161" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P161" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="162">
@@ -10786,11 +10786,11 @@
       </c>
       <c r="O162" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P162" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="163">
@@ -10848,11 +10848,11 @@
       </c>
       <c r="O163" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P163" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="164">
@@ -10910,11 +10910,11 @@
       </c>
       <c r="O164" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P164" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="165">
@@ -10972,11 +10972,11 @@
       </c>
       <c r="O165" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P165" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="166">
@@ -11034,11 +11034,11 @@
       </c>
       <c r="O166" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P166" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="167">
@@ -11096,11 +11096,11 @@
       </c>
       <c r="O167" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P167" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="168">
@@ -11158,11 +11158,11 @@
       </c>
       <c r="O168" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P168" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="169">
@@ -11220,11 +11220,11 @@
       </c>
       <c r="O169" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P169" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="170">
@@ -11282,11 +11282,11 @@
       </c>
       <c r="O170" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P170" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="171">
@@ -11344,11 +11344,11 @@
       </c>
       <c r="O171" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P171" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="172">
@@ -11406,11 +11406,11 @@
       </c>
       <c r="O172" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P172" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="173">
@@ -11468,11 +11468,11 @@
       </c>
       <c r="O173" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P173" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="174">
@@ -11530,11 +11530,11 @@
       </c>
       <c r="O174" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P174" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="175">
@@ -11592,11 +11592,11 @@
       </c>
       <c r="O175" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P175" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="176">
@@ -11654,11 +11654,11 @@
       </c>
       <c r="O176" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P176" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="177">
@@ -11716,11 +11716,11 @@
       </c>
       <c r="O177" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P177" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="178">
@@ -11778,11 +11778,11 @@
       </c>
       <c r="O178" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P178" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="179">
@@ -11840,11 +11840,11 @@
       </c>
       <c r="O179" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P179" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="180">
@@ -11902,11 +11902,11 @@
       </c>
       <c r="O180" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P180" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="181">
@@ -11964,11 +11964,11 @@
       </c>
       <c r="O181" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P181" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="182">
@@ -12026,11 +12026,11 @@
       </c>
       <c r="O182" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P182" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="183">
@@ -12088,11 +12088,11 @@
       </c>
       <c r="O183" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P183" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="184">
@@ -12150,11 +12150,11 @@
       </c>
       <c r="O184" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P184" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="185">
@@ -12212,11 +12212,11 @@
       </c>
       <c r="O185" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P185" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="186">
@@ -12274,11 +12274,11 @@
       </c>
       <c r="O186" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P186" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="187">
@@ -12336,11 +12336,11 @@
       </c>
       <c r="O187" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P187" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="188">
@@ -12398,11 +12398,11 @@
       </c>
       <c r="O188" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P188" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="189">
@@ -12460,11 +12460,11 @@
       </c>
       <c r="O189" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P189" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="190">
@@ -12522,11 +12522,11 @@
       </c>
       <c r="O190" s="69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P190" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="191">
@@ -12584,11 +12584,11 @@
       </c>
       <c r="O191" s="69" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P191" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="192">
@@ -12646,11 +12646,11 @@
       </c>
       <c r="O192" s="69" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P192" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="193">
@@ -12708,11 +12708,11 @@
       </c>
       <c r="O193" s="69" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P193" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="194">
@@ -12770,11 +12770,11 @@
       </c>
       <c r="O194" s="69" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P194" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="195">
@@ -12832,11 +12832,11 @@
       </c>
       <c r="O195" s="69" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P195" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="196">
@@ -12871,7 +12871,7 @@
       </c>
       <c r="H196" s="69" t="inlineStr">
         <is>
-          <t>021-1 BD40 - SM 021 - Digital input</t>
+          <t>021-1BD40 - SM 021 - Digital input</t>
         </is>
       </c>
       <c r="I196" s="69" t="n">
@@ -12894,11 +12894,11 @@
       </c>
       <c r="O196" s="69" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P196" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="197">
@@ -12933,7 +12933,7 @@
       </c>
       <c r="H197" s="69" t="inlineStr">
         <is>
-          <t>022-1 B890 - SM 022 - Digital output</t>
+          <t>022-1BB90 - SM 022 - Digital output</t>
         </is>
       </c>
       <c r="I197" s="69" t="n">
@@ -12956,11 +12956,11 @@
       </c>
       <c r="O197" s="69" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P197" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="198">
@@ -12995,7 +12995,7 @@
       </c>
       <c r="H198" s="69" t="inlineStr">
         <is>
-          <t>022-1 B890 - SM 022 - Digital output</t>
+          <t>022-1BB90 - SM 022 - Digital output</t>
         </is>
       </c>
       <c r="I198" s="69" t="n">
@@ -13018,11 +13018,11 @@
       </c>
       <c r="O198" s="69" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P198" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="199">
@@ -13057,7 +13057,7 @@
       </c>
       <c r="H199" s="69" t="inlineStr">
         <is>
-          <t>031-18B90 - SM 031 - Analog input</t>
+          <t>031-1BB90 - SM 031 - Analog input</t>
         </is>
       </c>
       <c r="I199" s="69" t="n">
@@ -13080,11 +13080,11 @@
       </c>
       <c r="O199" s="69" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P199" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="200">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="H200" s="69" t="inlineStr">
         <is>
-          <t>031-18B90 - SM 031 - Analog input</t>
+          <t>031-1BB90 - SM 031 - Analog input</t>
         </is>
       </c>
       <c r="I200" s="69" t="n">
@@ -13142,11 +13142,11 @@
       </c>
       <c r="O200" s="69" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P200" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="201">
@@ -13181,7 +13181,7 @@
       </c>
       <c r="H201" s="69" t="inlineStr">
         <is>
-          <t>031-18B90 - SM 031 - Analog input</t>
+          <t>031-1BB90 - SM 031 - Analog input</t>
         </is>
       </c>
       <c r="I201" s="69" t="n">
@@ -13204,11 +13204,11 @@
       </c>
       <c r="O201" s="69" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P201" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="202">
@@ -13243,7 +13243,7 @@
       </c>
       <c r="H202" s="69" t="inlineStr">
         <is>
-          <t>031-18B90 - SM 031 - Analog input</t>
+          <t>031-1BB90 - SM 031 - Analog input</t>
         </is>
       </c>
       <c r="I202" s="69" t="n">
@@ -13266,11 +13266,11 @@
       </c>
       <c r="O202" s="69" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P202" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="203">
@@ -13328,11 +13328,11 @@
       </c>
       <c r="O203" s="69" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P203" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="204">
@@ -13390,11 +13390,11 @@
       </c>
       <c r="O204" s="69" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P204" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="205">
@@ -13452,11 +13452,11 @@
       </c>
       <c r="O205" s="69" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P205" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="206">
@@ -13514,11 +13514,11 @@
       </c>
       <c r="O206" s="69" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P206" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="207">
@@ -13576,11 +13576,11 @@
       </c>
       <c r="O207" s="69" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P207" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="208">
@@ -13638,11 +13638,11 @@
       </c>
       <c r="O208" s="69" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P208" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="209">
@@ -13700,11 +13700,11 @@
       </c>
       <c r="O209" s="69" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P209" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="210">
@@ -13762,11 +13762,11 @@
       </c>
       <c r="O210" s="69" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P210" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="211">
@@ -13824,11 +13824,11 @@
       </c>
       <c r="O211" s="69" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P211" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="212">
@@ -13886,11 +13886,11 @@
       </c>
       <c r="O212" s="69" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P212" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="213">
@@ -13948,11 +13948,11 @@
       </c>
       <c r="O213" s="69" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P213" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="214">
@@ -14010,11 +14010,11 @@
       </c>
       <c r="O214" s="69" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P214" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="215">
@@ -14072,11 +14072,11 @@
       </c>
       <c r="O215" s="69" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P215" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="216">
@@ -14134,11 +14134,11 @@
       </c>
       <c r="O216" s="69" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P216" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="217">
@@ -14196,11 +14196,11 @@
       </c>
       <c r="O217" s="69" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P217" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="218">
@@ -14258,11 +14258,11 @@
       </c>
       <c r="O218" s="69" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P218" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="219">
@@ -14320,11 +14320,11 @@
       </c>
       <c r="O219" s="69" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P219" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="220">
@@ -14382,11 +14382,11 @@
       </c>
       <c r="O220" s="69" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P220" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="221">
@@ -14444,11 +14444,11 @@
       </c>
       <c r="O221" s="69" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P221" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="222">
@@ -14506,11 +14506,11 @@
       </c>
       <c r="O222" s="69" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P222" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="223">
@@ -14568,11 +14568,11 @@
       </c>
       <c r="O223" s="69" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P223" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="224">
@@ -14630,11 +14630,11 @@
       </c>
       <c r="O224" s="69" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P224" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="225">
@@ -14692,11 +14692,11 @@
       </c>
       <c r="O225" s="69" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P225" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="226">
@@ -14754,11 +14754,11 @@
       </c>
       <c r="O226" s="69" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P226" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="227">
@@ -14816,11 +14816,11 @@
       </c>
       <c r="O227" s="69" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P227" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="228">
@@ -14882,11 +14882,11 @@
       </c>
       <c r="O228" s="69" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
       <c r="P228" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="229">
@@ -14948,11 +14948,11 @@
       </c>
       <c r="O229" s="69" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>ses</t>
         </is>
       </c>
       <c r="P229" s="68" t="n">
-        <v>46316</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="230"/>
@@ -15105,7 +15105,7 @@
       </c>
       <c r="G2" s="75" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC)</t>
+          <t>955-CO00MO00 - VIPASetCard 001 (VSC)</t>
         </is>
       </c>
       <c r="H2" s="75" t="inlineStr"/>
@@ -15155,7 +15155,7 @@
       </c>
       <c r="G3" s="75" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC)</t>
+          <t>955-CO00MO00 - VIPASetCard 001 (VSC)</t>
         </is>
       </c>
       <c r="H3" s="75" t="inlineStr"/>
@@ -15313,7 +15313,7 @@
       </c>
       <c r="G6" s="75" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC)</t>
+          <t>955-CO000MO00 - VIPASetCard 001 (VSC)</t>
         </is>
       </c>
       <c r="H6" s="75" t="inlineStr"/>
@@ -16613,7 +16613,7 @@
       </c>
       <c r="G32" s="75" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC)</t>
+          <t>955-CO00M00 - VIPASetCard 001 (VSC)</t>
         </is>
       </c>
       <c r="H32" s="75" t="inlineStr"/>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="G33" s="75" t="inlineStr">
         <is>
-          <t>315-4NE23 -VIPA CPU 315SN</t>
+          <t>315-4NE23 - VIPA CPU 315SN</t>
         </is>
       </c>
       <c r="H33" s="75" t="inlineStr"/>
@@ -16713,7 +16713,7 @@
       </c>
       <c r="G34" s="75" t="inlineStr">
         <is>
-          <t>315-4NE23 -VIPA CPU 315SN</t>
+          <t>315-4NE23 - VIPA CPU 315SN</t>
         </is>
       </c>
       <c r="H34" s="75" t="inlineStr"/>
@@ -18013,7 +18013,7 @@
       </c>
       <c r="G60" s="75" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC)</t>
+          <t>955-COO00MO00 - VIPASetCard 001 (VSC)</t>
         </is>
       </c>
       <c r="H60" s="75" t="inlineStr"/>
@@ -24813,7 +24813,7 @@
       </c>
       <c r="G196" s="75" t="inlineStr">
         <is>
-          <t>021-1 BD40 - SM 021 - Digital input</t>
+          <t>021-1BD40 - SM 021 - Digital input</t>
         </is>
       </c>
       <c r="H196" s="75" t="inlineStr"/>
@@ -24863,7 +24863,7 @@
       </c>
       <c r="G197" s="75" t="inlineStr">
         <is>
-          <t>022-1 B890 - SM 022 - Digital output</t>
+          <t>022-1BB90 - SM 022 - Digital output</t>
         </is>
       </c>
       <c r="H197" s="75" t="inlineStr"/>
@@ -24913,7 +24913,7 @@
       </c>
       <c r="G198" s="75" t="inlineStr">
         <is>
-          <t>022-1 B890 - SM 022 - Digital output</t>
+          <t>022-1BB90 - SM 022 - Digital output</t>
         </is>
       </c>
       <c r="H198" s="75" t="inlineStr"/>
@@ -24963,7 +24963,7 @@
       </c>
       <c r="G199" s="75" t="inlineStr">
         <is>
-          <t>031-18B90 - SM 031 - Analog input</t>
+          <t>031-1BB90 - SM 031 - Analog input</t>
         </is>
       </c>
       <c r="H199" s="75" t="inlineStr"/>
@@ -25013,7 +25013,7 @@
       </c>
       <c r="G200" s="75" t="inlineStr">
         <is>
-          <t>031-18B90 - SM 031 - Analog input</t>
+          <t>031-1BB90 - SM 031 - Analog input</t>
         </is>
       </c>
       <c r="H200" s="75" t="inlineStr"/>
@@ -25063,7 +25063,7 @@
       </c>
       <c r="G201" s="75" t="inlineStr">
         <is>
-          <t>031-18B90 - SM 031 - Analog input</t>
+          <t>031-1BB90 - SM 031 - Analog input</t>
         </is>
       </c>
       <c r="H201" s="75" t="inlineStr"/>
@@ -25113,7 +25113,7 @@
       </c>
       <c r="G202" s="75" t="inlineStr">
         <is>
-          <t>031-18B90 - SM 031 - Analog input</t>
+          <t>031-1BB90 - SM 031 - Analog input</t>
         </is>
       </c>
       <c r="H202" s="75" t="inlineStr"/>
@@ -26521,7 +26521,7 @@
       </c>
       <c r="G230" s="75" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC)</t>
+          <t>955-CO00MO00 - VIPASetCard 001 (VSC)</t>
         </is>
       </c>
       <c r="H230" s="75" t="inlineStr"/>
@@ -26571,7 +26571,7 @@
       </c>
       <c r="G231" s="75" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC)</t>
+          <t>955-CO00MO00 - VIPASetCard 001 (VSC)</t>
         </is>
       </c>
       <c r="H231" s="75" t="inlineStr"/>
@@ -26729,7 +26729,7 @@
       </c>
       <c r="G234" s="75" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC)</t>
+          <t>955-CO000MO00 - VIPASetCard 001 (VSC)</t>
         </is>
       </c>
       <c r="H234" s="75" t="inlineStr"/>
@@ -28029,7 +28029,7 @@
       </c>
       <c r="G260" s="75" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC)</t>
+          <t>955-CO00M00 - VIPASetCard 001 (VSC)</t>
         </is>
       </c>
       <c r="H260" s="75" t="inlineStr"/>
@@ -28079,7 +28079,7 @@
       </c>
       <c r="G261" s="75" t="inlineStr">
         <is>
-          <t>315-4NE23 -VIPA CPU 315SN</t>
+          <t>315-4NE23 - VIPA CPU 315SN</t>
         </is>
       </c>
       <c r="H261" s="75" t="inlineStr"/>
@@ -28129,7 +28129,7 @@
       </c>
       <c r="G262" s="75" t="inlineStr">
         <is>
-          <t>315-4NE23 -VIPA CPU 315SN</t>
+          <t>315-4NE23 - VIPA CPU 315SN</t>
         </is>
       </c>
       <c r="H262" s="75" t="inlineStr"/>
@@ -29429,7 +29429,7 @@
       </c>
       <c r="G288" s="75" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC)</t>
+          <t>955-COO00MO00 - VIPASetCard 001 (VSC)</t>
         </is>
       </c>
       <c r="H288" s="75" t="inlineStr"/>
@@ -36229,7 +36229,7 @@
       </c>
       <c r="G424" s="75" t="inlineStr">
         <is>
-          <t>021-1 BD40 - SM 021 - Digital input</t>
+          <t>021-1BD40 - SM 021 - Digital input</t>
         </is>
       </c>
       <c r="H424" s="75" t="inlineStr"/>
@@ -36279,7 +36279,7 @@
       </c>
       <c r="G425" s="75" t="inlineStr">
         <is>
-          <t>022-1 B890 - SM 022 - Digital output</t>
+          <t>022-1BB90 - SM 022 - Digital output</t>
         </is>
       </c>
       <c r="H425" s="75" t="inlineStr"/>
@@ -36329,7 +36329,7 @@
       </c>
       <c r="G426" s="75" t="inlineStr">
         <is>
-          <t>022-1 B890 - SM 022 - Digital output</t>
+          <t>022-1BB90 - SM 022 - Digital output</t>
         </is>
       </c>
       <c r="H426" s="75" t="inlineStr"/>
@@ -36379,7 +36379,7 @@
       </c>
       <c r="G427" s="75" t="inlineStr">
         <is>
-          <t>031-18B90 - SM 031 - Analog input</t>
+          <t>031-1BB90 - SM 031 - Analog input</t>
         </is>
       </c>
       <c r="H427" s="75" t="inlineStr"/>
@@ -36429,7 +36429,7 @@
       </c>
       <c r="G428" s="75" t="inlineStr">
         <is>
-          <t>031-18B90 - SM 031 - Analog input</t>
+          <t>031-1BB90 - SM 031 - Analog input</t>
         </is>
       </c>
       <c r="H428" s="75" t="inlineStr"/>
@@ -36479,7 +36479,7 @@
       </c>
       <c r="G429" s="75" t="inlineStr">
         <is>
-          <t>031-18B90 - SM 031 - Analog input</t>
+          <t>031-1BB90 - SM 031 - Analog input</t>
         </is>
       </c>
       <c r="H429" s="75" t="inlineStr"/>
@@ -36529,7 +36529,7 @@
       </c>
       <c r="G430" s="75" t="inlineStr">
         <is>
-          <t>031-18B90 - SM 031 - Analog input</t>
+          <t>031-1BB90 - SM 031 - Analog input</t>
         </is>
       </c>
       <c r="H430" s="75" t="inlineStr"/>
@@ -39552,7 +39552,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>955-C000M00</t>
+          <t>955-CO00MO00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -39562,14 +39562,14 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/705</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>955-C000M00</t>
+          <t>955-CO00MO00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -39579,7 +39579,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/705</t>
         </is>
       </c>
     </row>
@@ -39600,7 +39600,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/708</t>
         </is>
       </c>
     </row>
@@ -39621,14 +39621,14 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/708</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>955-C000M00</t>
+          <t>955-CO000MO00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -39638,14 +39638,14 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/710</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -39655,14 +39655,14 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -39672,14 +39672,14 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -39689,14 +39689,14 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -39706,14 +39706,14 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -39723,14 +39723,14 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -39740,14 +39740,14 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -39757,14 +39757,14 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -39774,14 +39774,14 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -39791,14 +39791,14 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -39808,14 +39808,14 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -39825,14 +39825,14 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -39842,14 +39842,14 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -39859,14 +39859,14 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -39876,14 +39876,14 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -39893,14 +39893,14 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -39910,14 +39910,14 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -39927,14 +39927,14 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -39944,14 +39944,14 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -39961,14 +39961,14 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -39978,14 +39978,14 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -39995,14 +39995,14 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -40012,14 +40012,14 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -40029,14 +40029,14 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -40046,14 +40046,14 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -40063,14 +40063,14 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>955-C000M00</t>
+          <t>955-CO00M00</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -40080,7 +40080,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/711</t>
         </is>
       </c>
     </row>
@@ -40097,7 +40097,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/717</t>
         </is>
       </c>
     </row>
@@ -40114,14 +40114,14 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/717</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -40138,7 +40138,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -40155,7 +40155,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -40172,7 +40172,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -40189,7 +40189,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -40206,7 +40206,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -40223,7 +40223,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -40240,7 +40240,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -40257,7 +40257,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -40274,7 +40274,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -40291,7 +40291,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -40308,7 +40308,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -40325,7 +40325,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -40342,7 +40342,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -40359,7 +40359,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -40376,7 +40376,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -40393,7 +40393,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -40410,7 +40410,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -40427,7 +40427,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -40444,7 +40444,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -40461,7 +40461,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -40478,7 +40478,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -40495,7 +40495,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -40512,7 +40512,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -40529,7 +40529,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>015-CEFPR01</t>
+          <t>015-CEFPRO1</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -40546,7 +40546,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>955-C000M00</t>
+          <t>955-COO00MO00</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -40573,7 +40573,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40590,7 +40590,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40607,7 +40607,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40624,7 +40624,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40641,7 +40641,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40658,7 +40658,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40675,7 +40675,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40692,7 +40692,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40709,7 +40709,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40726,7 +40726,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40743,7 +40743,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40760,7 +40760,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40777,7 +40777,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40794,7 +40794,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40811,7 +40811,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40828,7 +40828,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40845,7 +40845,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40862,7 +40862,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40879,7 +40879,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40896,7 +40896,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40913,7 +40913,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40930,7 +40930,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40947,7 +40947,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40964,7 +40964,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40981,7 +40981,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -40998,7 +40998,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41015,7 +41015,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41032,7 +41032,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41049,7 +41049,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41066,7 +41066,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41083,7 +41083,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41100,7 +41100,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41117,7 +41117,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41134,7 +41134,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41151,7 +41151,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41168,7 +41168,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41185,7 +41185,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41202,7 +41202,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41219,7 +41219,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41236,7 +41236,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41253,7 +41253,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41270,7 +41270,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41287,7 +41287,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41304,7 +41304,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41321,7 +41321,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41338,7 +41338,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41355,7 +41355,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41372,7 +41372,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41389,7 +41389,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41406,7 +41406,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41423,7 +41423,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41440,7 +41440,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41457,7 +41457,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41474,7 +41474,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41491,7 +41491,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41508,7 +41508,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41525,7 +41525,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41542,7 +41542,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41559,7 +41559,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41576,7 +41576,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41593,7 +41593,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41610,7 +41610,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41627,7 +41627,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41644,7 +41644,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41661,7 +41661,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41678,7 +41678,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41695,7 +41695,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41712,7 +41712,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41729,7 +41729,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41746,7 +41746,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41763,7 +41763,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41780,7 +41780,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41797,7 +41797,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41814,7 +41814,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41831,7 +41831,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41848,7 +41848,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41865,7 +41865,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41882,7 +41882,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41899,7 +41899,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41916,7 +41916,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41933,7 +41933,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41950,7 +41950,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41967,7 +41967,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -41984,7 +41984,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42001,7 +42001,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42018,7 +42018,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42035,7 +42035,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42052,7 +42052,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42069,7 +42069,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42086,7 +42086,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42103,7 +42103,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42120,7 +42120,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42137,7 +42137,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42154,7 +42154,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42171,7 +42171,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42188,7 +42188,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42205,7 +42205,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42222,7 +42222,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42239,7 +42239,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42256,7 +42256,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42273,7 +42273,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42290,7 +42290,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42307,7 +42307,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42324,7 +42324,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42341,7 +42341,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42358,7 +42358,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42375,7 +42375,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42392,7 +42392,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42409,7 +42409,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42426,7 +42426,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42443,7 +42443,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42460,7 +42460,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42477,7 +42477,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42494,7 +42494,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42511,7 +42511,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42528,7 +42528,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42545,7 +42545,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42562,7 +42562,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42579,7 +42579,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42596,7 +42596,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42613,7 +42613,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42630,7 +42630,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42647,7 +42647,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42664,7 +42664,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42681,7 +42681,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42698,7 +42698,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42715,7 +42715,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42732,7 +42732,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42749,7 +42749,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42766,7 +42766,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>PO/V/712</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42783,7 +42783,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42800,7 +42800,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42817,7 +42817,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42834,7 +42834,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42851,7 +42851,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42868,7 +42868,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42885,7 +42885,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42902,7 +42902,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42919,7 +42919,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42936,7 +42936,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42953,7 +42953,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42970,7 +42970,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -42987,7 +42987,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43004,7 +43004,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43021,7 +43021,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43038,7 +43038,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43055,7 +43055,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43072,7 +43072,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43089,7 +43089,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43106,7 +43106,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43123,7 +43123,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43140,7 +43140,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43157,7 +43157,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43174,7 +43174,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43191,7 +43191,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43208,7 +43208,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43225,7 +43225,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43242,7 +43242,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43259,7 +43259,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43276,7 +43276,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43293,7 +43293,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43310,7 +43310,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43327,7 +43327,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43344,7 +43344,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43361,7 +43361,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43378,7 +43378,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43395,7 +43395,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43416,7 +43416,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>PO/V/718</t>
         </is>
       </c>
     </row>
@@ -43437,7 +43437,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>wer</t>
+          <t>ses</t>
         </is>
       </c>
     </row>
@@ -43457,7 +43457,7 @@
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="27" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
@@ -43717,7 +43717,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0 items from OCR</t>
+          <t>228 items from OCR</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -43803,7 +43803,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC) (Qty=1, Tot=10963.55)</t>
+          <t>955-CO00MO00 - VIPASetCard 001 (VSC) (Qty=1, Tot=10963.55)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -43818,7 +43818,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -43840,7 +43840,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC) (Qty=1, Tot=10963.55)</t>
+          <t>955-CO00MO00 - VIPASetCard 001 (VSC) (Qty=1, Tot=10963.55)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -43855,7 +43855,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -43892,7 +43892,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -43929,7 +43929,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -43951,7 +43951,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC) (Qty=1, Tot=10963.55)</t>
+          <t>955-CO000MO00 - VIPASetCard 001 (VSC) (Qty=1, Tot=10963.55)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -43966,7 +43966,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44003,7 +44003,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44040,7 +44040,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44077,7 +44077,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44114,7 +44114,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44151,7 +44151,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44188,7 +44188,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44225,7 +44225,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44262,7 +44262,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44299,7 +44299,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44336,7 +44336,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44373,7 +44373,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44410,7 +44410,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44447,7 +44447,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44484,7 +44484,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44521,7 +44521,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44558,7 +44558,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44595,7 +44595,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44632,7 +44632,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44669,7 +44669,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44706,7 +44706,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44743,7 +44743,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44780,7 +44780,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44817,7 +44817,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44854,7 +44854,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44891,7 +44891,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44913,7 +44913,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC) (Qty=1, Tot=10963.55)</t>
+          <t>955-CO00M00 - VIPASetCard 001 (VSC) (Qty=1, Tot=10963.55)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -44928,7 +44928,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44950,7 +44950,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>315-4NE23 -VIPA CPU 315SN (Qty=1, Tot=126780.98)</t>
+          <t>315-4NE23 - VIPA CPU 315SN (Qty=1, Tot=126780.98)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -44965,7 +44965,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -44987,7 +44987,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>315-4NE23 -VIPA CPU 315SN (Qty=1, Tot=126780.97)</t>
+          <t>315-4NE23 - VIPA CPU 315SN (Qty=1, Tot=126780.97)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -45002,7 +45002,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45039,7 +45039,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45076,7 +45076,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45113,7 +45113,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45150,7 +45150,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45187,7 +45187,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45224,7 +45224,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45261,7 +45261,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45298,7 +45298,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45335,7 +45335,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45372,7 +45372,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45409,7 +45409,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45446,7 +45446,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45483,7 +45483,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45520,7 +45520,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45557,7 +45557,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45594,7 +45594,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45631,7 +45631,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45668,7 +45668,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45705,7 +45705,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45742,7 +45742,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45779,7 +45779,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45816,7 +45816,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45853,7 +45853,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45890,7 +45890,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45927,7 +45927,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -45949,7 +45949,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>955-C000M00 - VIPASetCard 001 (VSC) (Qty=1, Tot=10963.55)</t>
+          <t>955-COO00MO00 - VIPASetCard 001 (VSC) (Qty=1, Tot=10963.55)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -45964,7 +45964,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46001,7 +46001,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46038,7 +46038,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46075,7 +46075,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46112,7 +46112,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46149,7 +46149,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46186,7 +46186,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46223,7 +46223,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46260,7 +46260,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46297,7 +46297,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46334,7 +46334,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46371,7 +46371,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46408,7 +46408,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46445,7 +46445,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46482,7 +46482,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46519,7 +46519,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46556,7 +46556,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46593,7 +46593,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46630,7 +46630,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46667,7 +46667,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46704,7 +46704,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46741,7 +46741,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46778,7 +46778,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46815,7 +46815,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46852,7 +46852,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46889,7 +46889,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46926,7 +46926,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -46963,7 +46963,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -47000,7 +47000,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -47037,7 +47037,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -47074,7 +47074,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -47111,7 +47111,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -47148,7 +47148,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -47185,7 +47185,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -47222,7 +47222,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -47259,7 +47259,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -47296,7 +47296,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -47333,7 +47333,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -47370,7 +47370,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -47407,7 +47407,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -47444,7 +47444,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -47481,7 +47481,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
